--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6569-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6569-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F68DF3D3-35E7-4610-A3E7-CF619EE66531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6592949-12DE-4F65-BFC5-B23A1FD196A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{94F3DF05-8284-49C6-904F-0C56A2B6E9EB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{4FB24918-935C-4F4B-B518-027BC2F29AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="6569-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1478,29 +1478,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41483933-D8F0-4FB0-A5E1-54D93FD15FB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4BFD06-4351-446C-97F9-FF648D0DF78A}">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1533,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1570,7 +1569,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1622,7 +1621,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1690,7 +1689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1762,7 +1761,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1834,7 +1833,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2122,7 +2121,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="40">
         <v>2018</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="42"/>
       <c r="B12" s="43"/>
       <c r="C12" s="18" t="s">
@@ -2222,7 +2221,7 @@
       <c r="W12" s="49"/>
       <c r="X12" s="45"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2017</v>
       </c>
@@ -2294,7 +2293,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2366,7 +2365,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2015</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2510,7 +2509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36" t="s">
         <v>39</v>
       </c>
